--- a/form_collection_templates/ros/Collection-Form-ROS-LL.xlsx
+++ b/form_collection_templates/ros/Collection-Form-ROS-LL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_collection_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B574AB-1B8B-7C4F-9A9F-8D2C45CD0961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AD9D2E-A07E-C24A-BCD9-DA2F5C95EB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12000" yWindow="740" windowWidth="17540" windowHeight="16680" tabRatio="872" activeTab="4" xr2:uid="{2052CEAD-15F2-4D91-9D69-B595B4741E8A}"/>
   </bookViews>
